--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1005,28 +1005,74 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="10" t="n"/>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="n"/>
-      <c r="M5" s="10" t="n"/>
-      <c r="N5" s="10" t="n"/>
-      <c r="O5" s="10" t="n"/>
-      <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="16" t="n"/>
-      <c r="R5" s="10" t="n"/>
-      <c r="S5" s="10" t="n"/>
-      <c r="T5" s="10" t="n"/>
-      <c r="U5" s="10" t="n"/>
-      <c r="V5" s="10" t="n"/>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>121.0391507537651</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>100.1605</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>64.02837938760268</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>2.51238109750737</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>-0.406</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q5" s="16" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>97.27</v>
+      </c>
+      <c r="S5" s="10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T5" s="10" t="n">
+        <v>4286.7</v>
+      </c>
+      <c r="U5" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V5" s="10" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1075,28 +1075,74 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="24" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="25" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
-      <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="24" t="n"/>
-      <c r="K6" s="24" t="n"/>
-      <c r="L6" s="24" t="n"/>
-      <c r="M6" s="24" t="n"/>
-      <c r="N6" s="24" t="n"/>
-      <c r="O6" s="24" t="n"/>
-      <c r="P6" s="24" t="n"/>
-      <c r="Q6" s="25" t="n"/>
-      <c r="R6" s="24" t="n"/>
-      <c r="S6" s="24" t="n"/>
-      <c r="T6" s="24" t="n"/>
-      <c r="U6" s="24" t="n"/>
-      <c r="V6" s="24" t="n"/>
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>121.0391507537651</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>100.1657</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>64.03032566477442</v>
+      </c>
+      <c r="J6" s="24" t="n">
+        <v>2.512082192904825</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="L6" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>-0.406</v>
+      </c>
+      <c r="N6" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" s="24" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="P6" s="24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q6" s="25" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R6" s="24" t="n">
+        <v>97.33199999999999</v>
+      </c>
+      <c r="S6" s="24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T6" s="24" t="n">
+        <v>4286.19</v>
+      </c>
+      <c r="U6" s="24" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V6" s="24" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1145,11 +1145,21 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n"/>
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="B7" s="18" t="n"/>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="16" t="n"/>
+      <c r="C7" s="24" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>121.0391507537651</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>2.5</v>
+      </c>
       <c r="F7" s="24" t="n"/>
       <c r="G7" s="24" t="n"/>
       <c r="H7" s="24" t="n"/>
@@ -1169,28 +1179,74 @@
       <c r="V7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="n"/>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-      <c r="I8" s="24" t="n"/>
-      <c r="J8" s="24" t="n"/>
-      <c r="K8" s="24" t="n"/>
-      <c r="L8" s="24" t="n"/>
-      <c r="M8" s="24" t="n"/>
-      <c r="N8" s="24" t="n"/>
-      <c r="O8" s="24" t="n"/>
-      <c r="P8" s="24" t="n"/>
-      <c r="Q8" s="16" t="n"/>
-      <c r="R8" s="24" t="n"/>
-      <c r="S8" s="24" t="n"/>
-      <c r="T8" s="24" t="n"/>
-      <c r="U8" s="24" t="n"/>
-      <c r="V8" s="24" t="n"/>
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>121.0391507537651</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>99.8707</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>63.48134055319773</v>
+      </c>
+      <c r="J8" s="24" t="n">
+        <v>2.54225983601273</v>
+      </c>
+      <c r="K8" s="24" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="L8" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" s="24" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="P8" s="24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q8" s="16" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R8" s="24" t="n">
+        <v>93.196</v>
+      </c>
+      <c r="S8" s="24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T8" s="24" t="n">
+        <v>4337.68</v>
+      </c>
+      <c r="U8" s="24" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V8" s="24" t="n">
+        <v>-0.14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="23" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据收集总表" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </numFmts>
   <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -56,8 +56,9 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <sz val="11"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -72,7 +73,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -140,22 +141,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE3F2FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -198,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -246,37 +232,28 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -640,12 +617,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="20"/>
-    <col width="11.26953125" customWidth="1" min="21" max="21"/>
-    <col width="11.08984375" customWidth="1" min="22" max="22"/>
+    <col width="11.25" customWidth="1" min="21" max="21"/>
+    <col width="11.125" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -873,731 +850,622 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n">
+        <v>838</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>122.57</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="P3" s="10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q3" s="16" t="n">
+        <v>297.27</v>
+      </c>
+      <c r="R3" s="10" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="S3" s="10" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T3" s="10" t="n">
+        <v>4543.41</v>
+      </c>
+      <c r="U3" s="10" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="V3" s="10" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B3" s="27" t="n">
+      <c r="B4" s="23" t="n">
         <v>838</v>
       </c>
-      <c r="C3" s="27" t="n">
+      <c r="C4" s="23" t="n">
         <v>4.88</v>
       </c>
-      <c r="D3" s="27" t="n">
+      <c r="D4" s="23" t="n">
         <v>122.56815</v>
       </c>
-      <c r="E3" s="28" t="n">
+      <c r="E4" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="F3" s="27" t="n">
+      <c r="F4" s="23" t="n">
         <v>1.95</v>
       </c>
-      <c r="G3" s="27" t="n">
+      <c r="G4" s="23" t="n">
         <v>97.7146</v>
       </c>
-      <c r="H3" s="27" t="n">
+      <c r="H4" s="23" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I3" s="27" t="n">
+      <c r="I4" s="23" t="n">
         <v>53.6281</v>
       </c>
-      <c r="J3" s="27" t="n">
+      <c r="J4" s="23" t="n">
         <v>3.3786</v>
       </c>
-      <c r="K3" s="27" t="n">
+      <c r="K4" s="23" t="n">
         <v>37.25</v>
       </c>
-      <c r="L3" s="27" t="n">
+      <c r="L4" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M4" s="23" t="n">
         <v>-0.0389</v>
       </c>
-      <c r="N3" s="27" t="n">
+      <c r="N4" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="O3" s="27" t="n">
+      <c r="O4" s="23" t="n">
         <v>18.38</v>
       </c>
-      <c r="P3" s="27" t="n">
+      <c r="P4" s="23" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q3" s="28" t="n">
+      <c r="Q4" s="24" t="n">
         <v>122.1733169555664</v>
       </c>
-      <c r="R3" s="27" t="n">
+      <c r="R4" s="23" t="n">
         <v>118.26</v>
       </c>
-      <c r="S3" s="27" t="n">
+      <c r="S4" s="23" t="n">
         <v>3.95</v>
       </c>
-      <c r="T3" s="27" t="n">
+      <c r="T4" s="23" t="n">
         <v>4730</v>
       </c>
-      <c r="U3" s="27" t="n">
+      <c r="U4" s="23" t="n">
         <v>-0.0978</v>
       </c>
-      <c r="V3" s="27" t="n">
+      <c r="V4" s="23" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="n">
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
         <v>870.5</v>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C5" s="23" t="n">
         <v>4.88</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D5" s="23" t="n">
         <v>121.0391507537651</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E5" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="F4" s="19" t="n"/>
-      <c r="G4" s="19" t="n">
-        <v>100.1393</v>
-      </c>
-      <c r="H4" s="19" t="n">
+      <c r="F5" s="23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>99.8814</v>
+      </c>
+      <c r="H5" s="23" t="n">
         <v>-1.53</v>
       </c>
-      <c r="I4" s="19" t="n">
-        <v>63.96214040840662</v>
-      </c>
-      <c r="J4" s="19" t="n">
-        <v>2.515030212808355</v>
-      </c>
-      <c r="K4" s="19" t="n"/>
-      <c r="L4" s="19" t="n">
+      <c r="I5" s="23" t="n">
+        <v>63.46985659935616</v>
+      </c>
+      <c r="J5" s="23" t="n">
+        <v>2.542171922894334</v>
+      </c>
+      <c r="K5" s="23" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="L5" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="M4" s="19" t="n"/>
-      <c r="N4" s="19" t="n">
+      <c r="M5" s="23" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="N5" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="O4" s="19" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="P4" s="19" t="n"/>
-      <c r="Q4" s="16" t="n">
+      <c r="O5" s="23" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="P5" s="23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q5" s="24" t="n">
         <v>184.18</v>
       </c>
-      <c r="R4" s="19" t="n">
-        <v>97.38800000000001</v>
-      </c>
-      <c r="S4" s="19" t="n">
+      <c r="R5" s="23" t="n">
+        <v>93.03100000000001</v>
+      </c>
+      <c r="S5" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="T4" s="19" t="n">
-        <v>4291.22</v>
-      </c>
-      <c r="U4" s="19" t="n">
+      <c r="T5" s="23" t="n">
+        <v>4337.53</v>
+      </c>
+      <c r="U5" s="23" t="n">
         <v>-0.01</v>
       </c>
-      <c r="V4" s="18" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>870.5</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>121.0391507537651</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>100.1605</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>64.02837938760268</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>2.51238109750737</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="L5" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M5" s="10" t="n">
-        <v>-0.406</v>
-      </c>
-      <c r="N5" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O5" s="10" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="P5" s="10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q5" s="16" t="n">
-        <v>184.18</v>
-      </c>
-      <c r="R5" s="10" t="n">
-        <v>97.27</v>
-      </c>
-      <c r="S5" s="10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T5" s="10" t="n">
-        <v>4286.7</v>
-      </c>
-      <c r="U5" s="10" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="V5" s="10" t="n">
-        <v>0.08</v>
+      <c r="V5" s="23" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="n">
-        <v>870.5</v>
-      </c>
-      <c r="C6" s="24" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="D6" s="24" t="n">
-        <v>121.0391507537651</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="G6" s="24" t="n">
-        <v>100.1657</v>
-      </c>
-      <c r="H6" s="24" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="I6" s="24" t="n">
-        <v>64.03032566477442</v>
-      </c>
-      <c r="J6" s="24" t="n">
-        <v>2.512082192904825</v>
-      </c>
-      <c r="K6" s="24" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="L6" s="24" t="n">
-        <v>50</v>
-      </c>
-      <c r="M6" s="24" t="n">
-        <v>-0.406</v>
-      </c>
-      <c r="N6" s="24" t="n">
-        <v>50</v>
-      </c>
-      <c r="O6" s="24" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="P6" s="24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q6" s="25" t="n">
-        <v>184.18</v>
-      </c>
-      <c r="R6" s="24" t="n">
-        <v>97.33199999999999</v>
-      </c>
-      <c r="S6" s="24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T6" s="24" t="n">
-        <v>4286.19</v>
-      </c>
-      <c r="U6" s="24" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="V6" s="24" t="n">
-        <v>0.09</v>
-      </c>
+      <c r="A6" s="22" t="n"/>
+      <c r="B6" s="23" t="n"/>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="23" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="24" t="n"/>
+      <c r="R6" s="23" t="n"/>
+      <c r="S6" s="23" t="n"/>
+      <c r="T6" s="23" t="n"/>
+      <c r="U6" s="23" t="n"/>
+      <c r="V6" s="23" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="24" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="D7" s="24" t="n">
-        <v>121.0391507537651</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="24" t="n"/>
-      <c r="H7" s="24" t="n"/>
-      <c r="I7" s="24" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="24" t="n"/>
-      <c r="L7" s="24" t="n"/>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="24" t="n"/>
-      <c r="O7" s="24" t="n"/>
-      <c r="P7" s="24" t="n"/>
-      <c r="Q7" s="16" t="n"/>
-      <c r="R7" s="24" t="n"/>
-      <c r="S7" s="24" t="n"/>
-      <c r="T7" s="24" t="n"/>
-      <c r="U7" s="24" t="n"/>
-      <c r="V7" s="24" t="n"/>
+      <c r="A7" s="22" t="n"/>
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="23" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="24" t="n"/>
+      <c r="R7" s="23" t="n"/>
+      <c r="S7" s="23" t="n"/>
+      <c r="T7" s="23" t="n"/>
+      <c r="U7" s="23" t="n"/>
+      <c r="V7" s="23" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>870.5</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>121.0391507537651</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>99.8707</v>
-      </c>
-      <c r="H8" s="24" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>63.48134055319773</v>
-      </c>
-      <c r="J8" s="24" t="n">
-        <v>2.54225983601273</v>
-      </c>
-      <c r="K8" s="24" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="L8" s="24" t="n">
-        <v>50</v>
-      </c>
-      <c r="M8" s="24" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="N8" s="24" t="n">
-        <v>50</v>
-      </c>
-      <c r="O8" s="24" t="n">
-        <v>24.76</v>
-      </c>
-      <c r="P8" s="24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q8" s="16" t="n">
-        <v>184.18</v>
-      </c>
-      <c r="R8" s="24" t="n">
-        <v>93.196</v>
-      </c>
-      <c r="S8" s="24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T8" s="24" t="n">
-        <v>4337.68</v>
-      </c>
-      <c r="U8" s="24" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="V8" s="24" t="n">
-        <v>-0.14</v>
-      </c>
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="23" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="24" t="n"/>
+      <c r="R8" s="23" t="n"/>
+      <c r="S8" s="23" t="n"/>
+      <c r="T8" s="23" t="n"/>
+      <c r="U8" s="23" t="n"/>
+      <c r="V8" s="23" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="24" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="24" t="n"/>
-      <c r="K9" s="24" t="n"/>
-      <c r="L9" s="24" t="n"/>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="24" t="n"/>
-      <c r="O9" s="24" t="n"/>
-      <c r="P9" s="24" t="n"/>
-      <c r="Q9" s="16" t="n"/>
-      <c r="R9" s="24" t="n"/>
-      <c r="S9" s="24" t="n"/>
-      <c r="T9" s="24" t="n"/>
-      <c r="U9" s="24" t="n"/>
-      <c r="V9" s="24" t="n"/>
+      <c r="A9" s="22" t="n"/>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="24" t="n"/>
+      <c r="R9" s="23" t="n"/>
+      <c r="S9" s="23" t="n"/>
+      <c r="T9" s="23" t="n"/>
+      <c r="U9" s="23" t="n"/>
+      <c r="V9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n"/>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
-      <c r="J10" s="24" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="24" t="n"/>
-      <c r="M10" s="24" t="n"/>
-      <c r="N10" s="24" t="n"/>
-      <c r="O10" s="24" t="n"/>
-      <c r="P10" s="24" t="n"/>
-      <c r="Q10" s="16" t="n"/>
-      <c r="R10" s="24" t="n"/>
-      <c r="S10" s="24" t="n"/>
-      <c r="T10" s="24" t="n"/>
-      <c r="U10" s="24" t="n"/>
-      <c r="V10" s="24" t="n"/>
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="23" t="n"/>
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="24" t="n"/>
+      <c r="R10" s="23" t="n"/>
+      <c r="S10" s="23" t="n"/>
+      <c r="T10" s="23" t="n"/>
+      <c r="U10" s="23" t="n"/>
+      <c r="V10" s="23" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="n"/>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="24" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="24" t="n"/>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="24" t="n"/>
-      <c r="O11" s="24" t="n"/>
-      <c r="P11" s="24" t="n"/>
-      <c r="Q11" s="16" t="n"/>
-      <c r="R11" s="24" t="n"/>
-      <c r="S11" s="24" t="n"/>
-      <c r="T11" s="24" t="n"/>
-      <c r="U11" s="24" t="n"/>
-      <c r="V11" s="24" t="n"/>
+      <c r="A11" s="22" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="23" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="24" t="n"/>
+      <c r="R11" s="23" t="n"/>
+      <c r="S11" s="23" t="n"/>
+      <c r="T11" s="23" t="n"/>
+      <c r="U11" s="23" t="n"/>
+      <c r="V11" s="23" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="n"/>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="24" t="n"/>
-      <c r="L12" s="24" t="n"/>
-      <c r="M12" s="24" t="n"/>
-      <c r="N12" s="24" t="n"/>
-      <c r="O12" s="24" t="n"/>
-      <c r="P12" s="24" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-      <c r="R12" s="24" t="n"/>
-      <c r="S12" s="24" t="n"/>
-      <c r="T12" s="24" t="n"/>
-      <c r="U12" s="24" t="n"/>
-      <c r="V12" s="24" t="n"/>
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="n"/>
+      <c r="M12" s="23" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="24" t="n"/>
+      <c r="R12" s="23" t="n"/>
+      <c r="S12" s="23" t="n"/>
+      <c r="T12" s="23" t="n"/>
+      <c r="U12" s="23" t="n"/>
+      <c r="V12" s="23" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n"/>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="24" t="n"/>
-      <c r="K13" s="24" t="n"/>
-      <c r="L13" s="24" t="n"/>
-      <c r="M13" s="24" t="n"/>
-      <c r="N13" s="24" t="n"/>
-      <c r="O13" s="24" t="n"/>
-      <c r="P13" s="24" t="n"/>
-      <c r="Q13" s="16" t="n"/>
-      <c r="R13" s="24" t="n"/>
-      <c r="S13" s="24" t="n"/>
-      <c r="T13" s="24" t="n"/>
-      <c r="U13" s="24" t="n"/>
-      <c r="V13" s="24" t="n"/>
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n"/>
+      <c r="M13" s="23" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="24" t="n"/>
+      <c r="R13" s="23" t="n"/>
+      <c r="S13" s="23" t="n"/>
+      <c r="T13" s="23" t="n"/>
+      <c r="U13" s="23" t="n"/>
+      <c r="V13" s="23" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n"/>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="24" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="24" t="n"/>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="24" t="n"/>
-      <c r="K14" s="24" t="n"/>
-      <c r="L14" s="24" t="n"/>
-      <c r="M14" s="24" t="n"/>
-      <c r="N14" s="24" t="n"/>
-      <c r="O14" s="24" t="n"/>
-      <c r="P14" s="24" t="n"/>
-      <c r="Q14" s="16" t="n"/>
-      <c r="R14" s="24" t="n"/>
-      <c r="S14" s="24" t="n"/>
-      <c r="T14" s="24" t="n"/>
-      <c r="U14" s="24" t="n"/>
-      <c r="V14" s="24" t="n"/>
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="23" t="n"/>
+      <c r="I14" s="23" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="23" t="n"/>
+      <c r="M14" s="23" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="24" t="n"/>
+      <c r="R14" s="23" t="n"/>
+      <c r="S14" s="23" t="n"/>
+      <c r="T14" s="23" t="n"/>
+      <c r="U14" s="23" t="n"/>
+      <c r="V14" s="23" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="n"/>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="24" t="n"/>
-      <c r="G15" s="24" t="n"/>
-      <c r="H15" s="24" t="n"/>
-      <c r="I15" s="24" t="n"/>
-      <c r="J15" s="24" t="n"/>
-      <c r="K15" s="24" t="n"/>
-      <c r="L15" s="24" t="n"/>
-      <c r="M15" s="24" t="n"/>
-      <c r="N15" s="24" t="n"/>
-      <c r="O15" s="24" t="n"/>
-      <c r="P15" s="24" t="n"/>
-      <c r="Q15" s="16">
-        <f>Q26</f>
-        <v/>
-      </c>
-      <c r="R15" s="24" t="n"/>
-      <c r="S15" s="24" t="n"/>
-      <c r="T15" s="24" t="n"/>
-      <c r="U15" s="24" t="n"/>
-      <c r="V15" s="24" t="n"/>
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="24" t="n"/>
+      <c r="R15" s="23" t="n"/>
+      <c r="S15" s="23" t="n"/>
+      <c r="T15" s="23" t="n"/>
+      <c r="U15" s="23" t="n"/>
+      <c r="V15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n"/>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="24" t="n"/>
-      <c r="G16" s="24" t="n"/>
-      <c r="H16" s="24" t="n"/>
-      <c r="I16" s="24" t="n"/>
-      <c r="J16" s="24" t="n"/>
-      <c r="K16" s="24" t="n"/>
-      <c r="L16" s="24" t="n"/>
-      <c r="M16" s="24" t="n"/>
-      <c r="N16" s="24" t="n"/>
-      <c r="O16" s="24" t="n"/>
-      <c r="P16" s="24" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-      <c r="R16" s="24" t="n"/>
-      <c r="S16" s="24" t="n"/>
-      <c r="T16" s="24" t="n"/>
-      <c r="U16" s="24" t="n"/>
-      <c r="V16" s="24" t="n"/>
+      <c r="A16" s="22" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="n"/>
+      <c r="I16" s="23" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="23" t="n"/>
+      <c r="L16" s="23" t="n"/>
+      <c r="M16" s="23" t="n"/>
+      <c r="N16" s="23" t="n"/>
+      <c r="O16" s="23" t="n"/>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="24" t="n"/>
+      <c r="R16" s="23" t="n"/>
+      <c r="S16" s="23" t="n"/>
+      <c r="T16" s="23" t="n"/>
+      <c r="U16" s="23" t="n"/>
+      <c r="V16" s="23" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="n"/>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="24" t="n"/>
-      <c r="H17" s="24" t="n"/>
-      <c r="I17" s="24" t="n"/>
-      <c r="J17" s="24" t="n"/>
-      <c r="K17" s="24" t="n"/>
-      <c r="L17" s="24" t="n"/>
-      <c r="M17" s="24" t="n"/>
-      <c r="N17" s="24" t="n"/>
-      <c r="O17" s="24" t="n"/>
-      <c r="P17" s="24" t="n"/>
-      <c r="Q17" s="16" t="n"/>
-      <c r="R17" s="24" t="n"/>
-      <c r="S17" s="24" t="n"/>
-      <c r="T17" s="24" t="n"/>
-      <c r="U17" s="24" t="n"/>
-      <c r="V17" s="24" t="n"/>
+      <c r="A17" s="22" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="23" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="23" t="n"/>
+      <c r="L17" s="23" t="n"/>
+      <c r="M17" s="23" t="n"/>
+      <c r="N17" s="23" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="24" t="n"/>
+      <c r="R17" s="23" t="n"/>
+      <c r="S17" s="23" t="n"/>
+      <c r="T17" s="23" t="n"/>
+      <c r="U17" s="23" t="n"/>
+      <c r="V17" s="23" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="10" t="n"/>
-      <c r="O18" s="10" t="n"/>
-      <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="16">
-        <f>Q27</f>
-        <v/>
-      </c>
-      <c r="R18" s="10" t="n"/>
-      <c r="S18" s="10" t="n"/>
-      <c r="T18" s="10" t="n"/>
-      <c r="U18" s="10" t="n"/>
-      <c r="V18" s="10" t="n"/>
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="n"/>
+      <c r="I18" s="23" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="23" t="n"/>
+      <c r="L18" s="23" t="n"/>
+      <c r="M18" s="23" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="23" t="n"/>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="24" t="n"/>
+      <c r="R18" s="23" t="n"/>
+      <c r="S18" s="23" t="n"/>
+      <c r="T18" s="23" t="n"/>
+      <c r="U18" s="23" t="n"/>
+      <c r="V18" s="23" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="16">
-        <f>Q28</f>
-        <v/>
-      </c>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="10" t="n"/>
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="23" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="23" t="n"/>
+      <c r="L19" s="23" t="n"/>
+      <c r="M19" s="23" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="24" t="n"/>
+      <c r="R19" s="23" t="n"/>
+      <c r="S19" s="23" t="n"/>
+      <c r="T19" s="23" t="n"/>
+      <c r="U19" s="23" t="n"/>
+      <c r="V19" s="23" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="10" t="n"/>
-      <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="16" t="n"/>
-      <c r="R20" s="10" t="n"/>
-      <c r="S20" s="10" t="n"/>
-      <c r="T20" s="10" t="n"/>
-      <c r="U20" s="10" t="n"/>
-      <c r="V20" s="10" t="n"/>
+      <c r="A20" s="22" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="n"/>
+      <c r="I20" s="23" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="23" t="n"/>
+      <c r="M20" s="23" t="n"/>
+      <c r="N20" s="23" t="n"/>
+      <c r="O20" s="23" t="n"/>
+      <c r="P20" s="23" t="n"/>
+      <c r="Q20" s="24" t="n"/>
+      <c r="R20" s="23" t="n"/>
+      <c r="S20" s="23" t="n"/>
+      <c r="T20" s="23" t="n"/>
+      <c r="U20" s="23" t="n"/>
+      <c r="V20" s="23" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="10" t="n"/>
-      <c r="N21" s="10" t="n"/>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="16">
-        <f>Q29</f>
-        <v/>
-      </c>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="10" t="n"/>
-      <c r="T21" s="10" t="n"/>
-      <c r="U21" s="10" t="n"/>
-      <c r="V21" s="10" t="n"/>
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="23" t="n"/>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="23" t="n"/>
+      <c r="L21" s="23" t="n"/>
+      <c r="M21" s="23" t="n"/>
+      <c r="N21" s="23" t="n"/>
+      <c r="O21" s="23" t="n"/>
+      <c r="P21" s="23" t="n"/>
+      <c r="Q21" s="24" t="n"/>
+      <c r="R21" s="23" t="n"/>
+      <c r="S21" s="23" t="n"/>
+      <c r="T21" s="23" t="n"/>
+      <c r="U21" s="23" t="n"/>
+      <c r="V21" s="23" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
-      <c r="M22" s="10" t="n"/>
-      <c r="N22" s="10" t="n"/>
-      <c r="O22" s="10" t="n"/>
-      <c r="P22" s="10" t="n"/>
-      <c r="Q22" s="16">
-        <f>Q30</f>
-        <v/>
-      </c>
-      <c r="R22" s="10" t="n"/>
-      <c r="S22" s="10" t="n"/>
-      <c r="T22" s="10" t="n"/>
-      <c r="U22" s="10" t="n"/>
-      <c r="V22" s="10" t="n"/>
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
+      <c r="L22" s="23" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="23" t="n"/>
+      <c r="O22" s="23" t="n"/>
+      <c r="P22" s="23" t="n"/>
+      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="23" t="n"/>
+      <c r="S22" s="23" t="n"/>
+      <c r="T22" s="23" t="n"/>
+      <c r="U22" s="23" t="n"/>
+      <c r="V22" s="23" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1639,7 +1507,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="6"/>
   </cols>
@@ -1734,7 +1602,10 @@
         <f>LOOKUP(2,1/(数据收集总表!C3:C31&lt;&gt;""),数据收集总表!C3:C31)</f>
         <v/>
       </c>
-      <c r="D6" s="10" t="n"/>
+      <c r="D6" s="10">
+        <f>IF(C6&gt;6,1,IF(C6&gt;=0,0,-1))</f>
+        <v/>
+      </c>
       <c r="E6" s="10">
         <f>D6*VALUE(SUBSTITUTE(B6,"%",""))/100</f>
         <v/>
@@ -1892,7 +1763,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="6"/>
   </cols>
@@ -2058,7 +1929,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="6"/>
   </cols>
@@ -2253,7 +2124,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="5"/>
   </cols>
@@ -2315,6 +2186,12 @@
         <f>LOOKUP(2,1/(数据收集总表!Q3:Q31&lt;&gt;""),数据收集总表!Q3:Q31)</f>
         <v/>
       </c>
+      <c r="C10" t="n">
+        <v>120</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2325,6 +2202,12 @@
       <c r="B11" s="13">
         <f>LOOKUP(2,1/(数据收集总表!R3:R31&lt;&gt;""),数据收集总表!R3:R31)</f>
         <v/>
+      </c>
+      <c r="C11" t="n">
+        <v>120</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -2360,7 +2243,7 @@
         </is>
       </c>
       <c r="B15" s="14">
-        <f>IF(B10&gt;120,IF(B11&gt;120,IF(B12&gt;4,1.2,IF(B13=-1,0.95,1.1)),IF(B11&gt;100,IF(B13=-1,0.95,1.1),1.1)),IF(B10&gt;100,IF(B11&gt;120,IF(B12&gt;4,1,IF(B13=-1,0.98,1.05)),IF(B11&gt;100,IF(B13=-1,0.98,1.05),1.05)),1))</f>
+        <f>IF(B10&gt;C10,IF(B11&gt;C11,IF(B12&gt;4,1.2,IF(B13=-1,0.95,1.1)),IF(B11&gt;D11,IF(B13=-1,0.95,1.1),1.1)),IF(B10&gt;D10,IF(B11&gt;C11,IF(B12&gt;4,1,IF(B13=-1,0.98,1.05)),IF(B11&gt;D11,IF(B13=-1,0.98,1.05),1.05)),1))</f>
         <v/>
       </c>
     </row>
@@ -2491,7 +2374,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="4"/>
   </cols>
@@ -2641,7 +2524,7 @@
           <t>原始信号</t>
         </is>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="25">
         <f>C4*C5*C6*C7*C8</f>
         <v/>
       </c>
@@ -2663,7 +2546,7 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <f>IF(强制规则检查表!E2&lt;&gt;"","触发","未触发")</f>
+        <f>IF(强制规则检查表!E2&lt;&gt;"","触发",IF(强制规则检查表!E3&lt;&gt;"","触发",IF(强制规则检查表!E4&lt;&gt;"","触发",IF(强制规则检查表!E5&lt;&gt;"","触发","未触发"))))</f>
         <v/>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -2683,8 +2566,8 @@
           <t>最终信号</t>
         </is>
       </c>
-      <c r="C11" s="20">
-        <f>IF(强制规则检查表!E2&lt;&gt;"",强制规则检查表!D2,C9)</f>
+      <c r="C11" s="25">
+        <f>IF(强制规则检查表!E2&lt;&gt;"",强制规则检查表!D2,IF(强制规则检查表!E3&lt;&gt;"",强制规则检查表!D3,IF(强制规则检查表!E4&lt;&gt;"",强制规则检查表!D4,IF(强制规则检查表!E5&lt;&gt;"",强制规则检查表!D5,C9))))</f>
         <v/>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -2829,7 +2712,7 @@
           <t>建议仓位:</t>
         </is>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <f>IF(C11&gt;=0.6,B15,IF(C11&gt;=0.35,B16,IF(C11&gt;=0.15,B17,IF(C11&gt;=-0.15,B18,IF(C11&gt;=-0.35,B19,B20)))))</f>
         <v/>
       </c>
@@ -2846,7 +2729,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="5"/>
   </cols>
@@ -2890,14 +2773,14 @@
         </is>
       </c>
       <c r="C2" s="10">
-        <f>AND(流动性地缘乘数表!B3&gt;=35,数据收集总表!#REF!&lt;=-0.01,数据收集总表!#REF!&gt;=0.005)</f>
+        <f>AND(流动性地缘乘数表!B3&gt;=35,LOOKUP(2,1/(数据收集总表!U3:U31&lt;&gt;""),数据收集总表!U3:U31)&lt;=-0.01,LOOKUP(2,1/(数据收集总表!V3:V31&lt;&gt;""),数据收集总表!V3:V31)&gt;=0.005)</f>
         <v/>
       </c>
       <c r="D2" s="10" t="n">
         <v>-0.5</v>
       </c>
       <c r="E2" s="10">
-        <f>IF(C2=TRUE,"触发","")</f>
+        <f>IF(C2=TRUE,D2,"")</f>
         <v/>
       </c>
     </row>
@@ -2920,7 +2803,7 @@
         <v>-0.2</v>
       </c>
       <c r="E3" s="10">
-        <f>IF(C3=TRUE,"触发","")</f>
+        <f>IF(C3=TRUE,D3,"")</f>
         <v/>
       </c>
     </row>
@@ -2943,7 +2826,7 @@
         <v>0.3</v>
       </c>
       <c r="E4" s="10">
-        <f>IF(C4=TRUE,"触发","")</f>
+        <f>IF(C4=TRUE,D4,"")</f>
         <v/>
       </c>
     </row>
@@ -2966,7 +2849,7 @@
         <v>0.15</v>
       </c>
       <c r="E5" s="10">
-        <f>IF(C5=TRUE,"触发","")</f>
+        <f>IF(C5=TRUE,D5,"")</f>
         <v/>
       </c>
     </row>
@@ -2981,8 +2864,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="8"/>
   </cols>
@@ -3030,373 +2913,117 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>首次数据收集</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>完成20项数据采集与填充</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>S_macro=-0.25, K_verif=0.85, K_trend=0.94, 最终信号=-0.20</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="inlineStr">
-        <is>
-          <t>中性偏空，等待回调</t>
-        </is>
-      </c>
+      <c r="A2" s="17" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
       <c r="F2" s="13" t="n"/>
       <c r="G2" s="13" t="n"/>
       <c r="H2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>完成21项数据采集</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>S_macro: 央行购金=838吨, M2=4.2%, 债务GDP=122.57%, Fed=-15bp, TIPS=1.92%, DXY=98.66</t>
-        </is>
-      </c>
+      <c r="A3" s="13" t="n"/>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
       <c r="F3" s="13" t="n"/>
       <c r="G3" s="13" t="n"/>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>自动收集2026-04-30 17:25 | 数据源:新浪/Stooq/FRED/TradingEconomics/akshare(GC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>2026-04-30 18:34:08</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>自动数据收集</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Row 6 (2026-04-30)</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>22/22项数据完整写入</t>
-        </is>
-      </c>
+      <c r="H3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
       <c r="F4" s="13" t="n"/>
       <c r="G4" s="13" t="n"/>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>数据源: 新浪(金价/银价/金银比/DXY日涨跌), Stooq(DXY), FRED(M2/TIPS/债务GDP/VIX/信用利差/CPI), TradingEconomics(布油$110.37), akshare COMEX GC(技术指标/ETF变化), 缓存(GPR/AISC/央行购金/Fed预期差)</t>
-        </is>
-      </c>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-30 19:45:11</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>自动数据收集</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Row 7 (2026-04-30)</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>22/22项数据完整写入</t>
-        </is>
-      </c>
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
       <c r="F5" s="13" t="n"/>
       <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>数据源: 新浪(hf_XAU/hf_XAG/hf_CL金价/银价/金银比), Stooq(DXY=98.485), FRED(M2=4.2%/TIPS=1.92%/债务GDP=122.57%/VIX=17.83/信用利差=1.69%/CPI=3.32%), akshare COMEX GC(技术指标), 东方财富(ETF4周变化=1.8%), 缓存(GPR=297.27/AISC=1400/央行购金=838吨/Fed=-15bp)</t>
-        </is>
-      </c>
+      <c r="H5" s="13" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-30 20:51:46</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>自动数据收集</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>数据收集总表 Row 8</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>新增2026-04-30数据，22项全部完整</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
       <c r="F6" s="13" t="n"/>
       <c r="G6" s="13" t="n"/>
       <c r="H6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-30 21:59:13</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>自动数据收集</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>数据收集总表 Row 9</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>新增2026-04-30数据，22项全部完整</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>金价$4543.41, DXY=98.327, VIX=18.81, GPR=297.27</t>
-        </is>
-      </c>
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
       <c r="F7" s="13" t="n"/>
       <c r="G7" s="13" t="n"/>
       <c r="H7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-30 23:05:30</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>自动数据收集</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>数据收集总表 Row 10 (2026-04-30)</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>新增2026-04-30数据行，22项全部完整</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
       <c r="F8" s="13" t="n"/>
       <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>数据源: 新浪(hf_XAU金价4543.41/hf_XAG银价71.27/金银比63.75/hf_CL WTI原油106.263/ETF技术指标), Stooq(DXY=98.005), FRED(M2=4.2%/TIPS=1.92%/债务GDP=122.57%/VIX=18.81/信用利差=1.69%/CPI同比=3.12%), 东方财富(ETF4周变化=2.17%), 缓存(GPR=297.27/AISC=1400/央行购金=838吨/Fed=-15bp)</t>
-        </is>
-      </c>
+      <c r="H8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>第2026-05-01行</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>填充 21/22 字段</t>
-        </is>
-      </c>
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
       <c r="F9" s="13" t="n"/>
       <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>自动化任务执行 02:24:09</t>
-        </is>
-      </c>
+      <c r="H9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>第2026-05-01行</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>填充 21/22 字段</t>
-        </is>
-      </c>
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>自动化任务执行 06:31:28</t>
-        </is>
-      </c>
+      <c r="H10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>第2026-05-01行</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>填充 21/22 字段</t>
-        </is>
-      </c>
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>自动化任务执行 06:51:20</t>
-        </is>
-      </c>
+      <c r="H11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>第2026-05-01行</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>填充 21/22 字段</t>
-        </is>
-      </c>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
       <c r="F12" s="13" t="n"/>
       <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>自动化任务执行 07:56:30</t>
-        </is>
-      </c>
+      <c r="H12" s="13" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-01 14:38:38 | 自动更新 | 新增第16行数据 | 22/22项完整 | 金价$4595.08 DXY 98.232 布油$111.815 | 来源: 新浪+FRED+CNBC+东方财富</t>
-        </is>
-      </c>
+      <c r="A13" s="13" t="n"/>
       <c r="B13" s="13" t="n"/>
       <c r="C13" s="13" t="n"/>
       <c r="D13" s="13" t="n"/>
@@ -3406,280 +3033,84 @@
       <c r="H13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-12 08:16:50</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>自动更新数据</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>dxy, aisc</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>自动收集20/22项数据</t>
-        </is>
-      </c>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
       <c r="F14" s="13" t="n"/>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>自动更新</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>17项数据</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Row 14</t>
-        </is>
-      </c>
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
       <c r="F15" s="13" t="n"/>
       <c r="G15" s="13" t="n"/>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>自动采集 17 项数据，缺失: 金价, AISC, ETF4周变化</t>
-        </is>
-      </c>
+      <c r="H15" s="13" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>自动更新</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>20项数据</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Row 15</t>
-        </is>
-      </c>
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>自动采集 20 项数据，缺失: AISC, ETF4周变化</t>
-        </is>
-      </c>
+      <c r="H16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>自动更新</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>22项数据</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Row 16</t>
-        </is>
-      </c>
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
       <c r="F17" s="13" t="n"/>
       <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>自动采集 22 项数据，缺失: AISC</t>
-        </is>
-      </c>
+      <c r="H17" s="13" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>自动更新</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>22项数据</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Row 17</t>
-        </is>
-      </c>
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>自动采集 22 项数据，缺失: AISC</t>
-        </is>
-      </c>
+      <c r="H18" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-13 08:36:01</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>自动更新</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>GMVM_v6.1_数据表 第14行(2026-05-13)</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>22/22项原始数据采集完成</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>自动采集22项: 金价730(akshare GC), 银价8.20(akshare SI), DXY=97.7146(FRED/1.208 05-08), 布油18.26(FRED 05-01), M2同比=4.88%, TIPS=1.95%, VIX=18.38, 信用利差=1.65%, 债务/GDP=122.57%, CPI同比=3.95%, Fed预期差=2.5bp(SOFR), GPR=122.17(04月), 央行购金=838吨(Q1-2026缓存), RSI=37.25, 布林带=67, MACD背离=50, MA20斜率=-0.04%, ETF4周=-0.01%, 金银比=53.63, 金价日涨跌=-0.10%, DXY日涨跌=0.00%(FRED尚未更新); AISC字段待手动从WGC更新</t>
-        </is>
-      </c>
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-13 15:58:50</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>每日轻量</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>8+7项</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Row15</t>
-        </is>
-      </c>
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
       <c r="F20" s="13" t="n"/>
       <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>每日轻量采集8项，继承7项低频数据</t>
-        </is>
-      </c>
+      <c r="H20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-13 15:59:33</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>低频补全</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>7项</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Row15</t>
-        </is>
-      </c>
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
       <c r="F21" s="13" t="n"/>
       <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>补全:央行购金=838吨,AISC=$1400.0,GPR=122.1733169555664,M2同比=4.88%,债务/GDP=122.56815%,CPI同比=3.95%,信用利差=1.65%</t>
-        </is>
-      </c>
+      <c r="H21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="n"/>
@@ -3751,479 +3182,6 @@
       <c r="G28" s="13" t="n"/>
       <c r="H28" s="13" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-05-01 00:11:24</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>数据更新</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>新增Row 11</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>22/22项完整</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-05-01 01:17:10</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>数据收集总表</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>自动更新第29行 (2026-05-01)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>03:33:25</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>自动收集数据 (行11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>03:35:42</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>自动化数据收集 (行6, 22字段完整)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-05-01 04:40:08</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>自动数据收集</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>数据收集总表 Row 6 (2026-05-01)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>22/22项数据完整更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-05-01 05:42:00</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>自动数据收集</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>数据收集总表 Row 7 (2026-05-01)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>22/22项数据完整写入</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>自动化任务执行 06:51:20 (已补充布油价格110.44)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>07:58:23</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>第11行</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>22/22项数据完整写入</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>09:08:27</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>第12行</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>22/22项数据完整写入</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10:12:58</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>第13行</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>21/22项数据完整写入</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10:13:26</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>补充数据</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>第13行</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>TIPS=1.96, CPI同比=3.32% 补充完整 (22/22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>11:15:45</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>第14行</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>22/22项数据完整写入</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>12:22:38</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>第15行</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>21/22项数据完整写入</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>12:24:14</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>补充数据</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>第15行</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>CPI同比=3.32% 补充完整 (22/22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:58:33</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>第17行</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>22/22项数据完整写入</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>23:04:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>数据收集</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>第18行</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>22/22项完整 (DXY已修正为97.911)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-05-09 11:40:22</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>自动采集: 新增5行数据(2026-05-04至2026-05-08)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>数据来源: akshare(GC/SI期货)、东方财富UDI(DXY)、东方财富B00Y(布油)、FRED(TIPS/VIX/信用利差/M2/CPI)、GPR月度2026-04(matteoiacoviello.com)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-05-11 08:17:48</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>自动采集写入 2026-05-11 数据行（金价=4694.6, DXY=98.01, 布油=104.66）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-05-11 16:02:52</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>自动采集更新 2026-05-11 数据（金价=4683.5, DXY=97.9845, 布油=104.91, 银价=80.895, RSI=47.63）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-05-13 17:32:51</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>风险预警</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>信号等级</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>中性偏空 (-0.20)</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>偏空 (-0.27482751)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>等级变化: 中性偏空→偏空</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1060,76 +1060,214 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="23" t="n"/>
-      <c r="I6" s="23" t="n"/>
-      <c r="J6" s="23" t="n"/>
-      <c r="K6" s="23" t="n"/>
-      <c r="L6" s="23" t="n"/>
-      <c r="M6" s="23" t="n"/>
-      <c r="N6" s="23" t="n"/>
-      <c r="O6" s="23" t="n"/>
-      <c r="P6" s="23" t="n"/>
-      <c r="Q6" s="24" t="n"/>
-      <c r="R6" s="23" t="n"/>
-      <c r="S6" s="23" t="n"/>
-      <c r="T6" s="23" t="n"/>
-      <c r="U6" s="23" t="n"/>
-      <c r="V6" s="23" t="n"/>
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>121.0391507537651</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>99.58069999999999</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="I6" s="23" t="n">
+        <v>61.56693582660434</v>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>2.547141944520961</v>
+      </c>
+      <c r="K6" s="23" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="L6" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M6" s="23" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="N6" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" s="23" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="P6" s="23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q6" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R6" s="23" t="n">
+        <v>81.437</v>
+      </c>
+      <c r="S6" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T6" s="23" t="n">
+        <v>4346.01</v>
+      </c>
+      <c r="U6" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V6" s="23" t="n">
+        <v>-0.09</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="23" t="n"/>
-      <c r="H7" s="23" t="n"/>
-      <c r="I7" s="23" t="n"/>
-      <c r="J7" s="23" t="n"/>
-      <c r="K7" s="23" t="n"/>
-      <c r="L7" s="23" t="n"/>
-      <c r="M7" s="23" t="n"/>
-      <c r="N7" s="23" t="n"/>
-      <c r="O7" s="23" t="n"/>
-      <c r="P7" s="23" t="n"/>
-      <c r="Q7" s="24" t="n"/>
-      <c r="R7" s="23" t="n"/>
-      <c r="S7" s="23" t="n"/>
-      <c r="T7" s="23" t="n"/>
-      <c r="U7" s="23" t="n"/>
-      <c r="V7" s="23" t="n"/>
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>121.0391507537651</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>99.58150000000001</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="I7" s="23" t="n">
+        <v>61.57942468471022</v>
+      </c>
+      <c r="J7" s="23" t="n">
+        <v>2.546936813911372</v>
+      </c>
+      <c r="K7" s="23" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="L7" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M7" s="23" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="N7" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O7" s="23" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="P7" s="23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q7" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R7" s="23" t="n">
+        <v>81.423</v>
+      </c>
+      <c r="S7" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T7" s="23" t="n">
+        <v>4345.66</v>
+      </c>
+      <c r="U7" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V7" s="23" t="n">
+        <v>-0.09</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="23" t="n"/>
-      <c r="G8" s="23" t="n"/>
-      <c r="H8" s="23" t="n"/>
-      <c r="I8" s="23" t="n"/>
-      <c r="J8" s="23" t="n"/>
-      <c r="K8" s="23" t="n"/>
-      <c r="L8" s="23" t="n"/>
-      <c r="M8" s="23" t="n"/>
-      <c r="N8" s="23" t="n"/>
-      <c r="O8" s="23" t="n"/>
-      <c r="P8" s="23" t="n"/>
-      <c r="Q8" s="24" t="n"/>
-      <c r="R8" s="23" t="n"/>
-      <c r="S8" s="23" t="n"/>
-      <c r="T8" s="23" t="n"/>
-      <c r="U8" s="23" t="n"/>
-      <c r="V8" s="23" t="n"/>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>121.0391507537651</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>99.6054</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>61.6081713718258</v>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>2.545237160289058</v>
+      </c>
+      <c r="K8" s="23" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="L8" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M8" s="23" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="N8" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" s="23" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="P8" s="23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q8" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R8" s="23" t="n">
+        <v>81.342</v>
+      </c>
+      <c r="S8" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T8" s="23" t="n">
+        <v>4342.76</v>
+      </c>
+      <c r="U8" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V8" s="23" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1270,28 +1270,74 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="23" t="n"/>
-      <c r="H9" s="23" t="n"/>
-      <c r="I9" s="23" t="n"/>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="23" t="n"/>
-      <c r="L9" s="23" t="n"/>
-      <c r="M9" s="23" t="n"/>
-      <c r="N9" s="23" t="n"/>
-      <c r="O9" s="23" t="n"/>
-      <c r="P9" s="23" t="n"/>
-      <c r="Q9" s="24" t="n"/>
-      <c r="R9" s="23" t="n"/>
-      <c r="S9" s="23" t="n"/>
-      <c r="T9" s="23" t="n"/>
-      <c r="U9" s="23" t="n"/>
-      <c r="V9" s="23" t="n"/>
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>122.7720900641192</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>101.065</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="I9" s="23" t="n">
+        <v>65.93630980956952</v>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>2.41489131008129</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="L9" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M9" s="23" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="N9" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" s="23" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="P9" s="23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q9" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R9" s="23" t="n">
+        <v>76.65900000000001</v>
+      </c>
+      <c r="S9" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T9" s="23" t="n">
+        <v>4120.36</v>
+      </c>
+      <c r="U9" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V9" s="23" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1340,28 +1340,74 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="23" t="n"/>
-      <c r="H10" s="23" t="n"/>
-      <c r="I10" s="23" t="n"/>
-      <c r="J10" s="23" t="n"/>
-      <c r="K10" s="23" t="n"/>
-      <c r="L10" s="23" t="n"/>
-      <c r="M10" s="23" t="n"/>
-      <c r="N10" s="23" t="n"/>
-      <c r="O10" s="23" t="n"/>
-      <c r="P10" s="23" t="n"/>
-      <c r="Q10" s="24" t="n"/>
-      <c r="R10" s="23" t="n"/>
-      <c r="S10" s="23" t="n"/>
-      <c r="T10" s="23" t="n"/>
-      <c r="U10" s="23" t="n"/>
-      <c r="V10" s="23" t="n"/>
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>122.7720900641192</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>101.602</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="I10" s="23" t="n">
+        <v>66.57941176470588</v>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>2.388107113343453</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="L10" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M10" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N10" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O10" s="23" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="P10" s="23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q10" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R10" s="23" t="n">
+        <v>75.508</v>
+      </c>
+      <c r="S10" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T10" s="23" t="n">
+        <v>4074.66</v>
+      </c>
+      <c r="U10" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V10" s="23" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1410,28 +1410,74 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="23" t="n"/>
-      <c r="H11" s="23" t="n"/>
-      <c r="I11" s="23" t="n"/>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="23" t="n"/>
-      <c r="M11" s="23" t="n"/>
-      <c r="N11" s="23" t="n"/>
-      <c r="O11" s="23" t="n"/>
-      <c r="P11" s="23" t="n"/>
-      <c r="Q11" s="24" t="n"/>
-      <c r="R11" s="23" t="n"/>
-      <c r="S11" s="23" t="n"/>
-      <c r="T11" s="23" t="n"/>
-      <c r="U11" s="23" t="n"/>
-      <c r="V11" s="23" t="n"/>
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>122.7720900641192</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>101.6082</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="I11" s="23" t="n">
+        <v>66.633627739614</v>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>2.387708573873393</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="L11" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M11" s="23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N11" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O11" s="23" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="P11" s="23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q11" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R11" s="23" t="n">
+        <v>75.337</v>
+      </c>
+      <c r="S11" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T11" s="23" t="n">
+        <v>4073.98</v>
+      </c>
+      <c r="U11" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V11" s="23" t="n">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1480,28 +1480,74 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
-      <c r="H12" s="23" t="n"/>
-      <c r="I12" s="23" t="n"/>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="23" t="n"/>
-      <c r="L12" s="23" t="n"/>
-      <c r="M12" s="23" t="n"/>
-      <c r="N12" s="23" t="n"/>
-      <c r="O12" s="23" t="n"/>
-      <c r="P12" s="23" t="n"/>
-      <c r="Q12" s="24" t="n"/>
-      <c r="R12" s="23" t="n"/>
-      <c r="S12" s="23" t="n"/>
-      <c r="T12" s="23" t="n"/>
-      <c r="U12" s="23" t="n"/>
-      <c r="V12" s="23" t="n"/>
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>122.7720900641192</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>101.485</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>69.82791754018169</v>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>2.34256225714001</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="L12" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" s="23" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O12" s="23" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="P12" s="23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q12" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R12" s="23" t="n">
+        <v>72.825</v>
+      </c>
+      <c r="S12" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T12" s="23" t="n">
+        <v>3996.95</v>
+      </c>
+      <c r="U12" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V12" s="23" t="n">
+        <v>-0.09</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1550,28 +1550,74 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="23" t="n"/>
-      <c r="H13" s="23" t="n"/>
-      <c r="I13" s="23" t="n"/>
-      <c r="J13" s="23" t="n"/>
-      <c r="K13" s="23" t="n"/>
-      <c r="L13" s="23" t="n"/>
-      <c r="M13" s="23" t="n"/>
-      <c r="N13" s="23" t="n"/>
-      <c r="O13" s="23" t="n"/>
-      <c r="P13" s="23" t="n"/>
-      <c r="Q13" s="24" t="n"/>
-      <c r="R13" s="23" t="n"/>
-      <c r="S13" s="23" t="n"/>
-      <c r="T13" s="23" t="n"/>
-      <c r="U13" s="23" t="n"/>
-      <c r="V13" s="23" t="n"/>
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>122.7720900641192</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>101.4852</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I13" s="23" t="n">
+        <v>69.6426080892608</v>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>2.341243560364077</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="L13" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M13" s="23" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="N13" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O13" s="23" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="P13" s="23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q13" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R13" s="23" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="S13" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T13" s="23" t="n">
+        <v>3994.7</v>
+      </c>
+      <c r="U13" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V13" s="23" t="n">
+        <v>-0.09</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1620,28 +1620,74 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="24" t="n"/>
-      <c r="F14" s="23" t="n"/>
-      <c r="G14" s="23" t="n"/>
-      <c r="H14" s="23" t="n"/>
-      <c r="I14" s="23" t="n"/>
-      <c r="J14" s="23" t="n"/>
-      <c r="K14" s="23" t="n"/>
-      <c r="L14" s="23" t="n"/>
-      <c r="M14" s="23" t="n"/>
-      <c r="N14" s="23" t="n"/>
-      <c r="O14" s="23" t="n"/>
-      <c r="P14" s="23" t="n"/>
-      <c r="Q14" s="24" t="n"/>
-      <c r="R14" s="23" t="n"/>
-      <c r="S14" s="23" t="n"/>
-      <c r="T14" s="23" t="n"/>
-      <c r="U14" s="23" t="n"/>
-      <c r="V14" s="23" t="n"/>
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-25 04:13:02</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>122.7720900641192</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>101.4776</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I14" s="23" t="n">
+        <v>69.57932357043236</v>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>2.339116062898906</v>
+      </c>
+      <c r="K14" s="23" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="L14" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M14" s="23" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="N14" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O14" s="23" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="P14" s="23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q14" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R14" s="23" t="n">
+        <v>72.85899999999999</v>
+      </c>
+      <c r="S14" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T14" s="23" t="n">
+        <v>3991.07</v>
+      </c>
+      <c r="U14" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V14" s="23" t="n">
+        <v>-0.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1690,28 +1690,74 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="n"/>
-      <c r="H15" s="23" t="n"/>
-      <c r="I15" s="23" t="n"/>
-      <c r="J15" s="23" t="n"/>
-      <c r="K15" s="23" t="n"/>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="23" t="n"/>
-      <c r="N15" s="23" t="n"/>
-      <c r="O15" s="23" t="n"/>
-      <c r="P15" s="23" t="n"/>
-      <c r="Q15" s="24" t="n"/>
-      <c r="R15" s="23" t="n"/>
-      <c r="S15" s="23" t="n"/>
-      <c r="T15" s="23" t="n"/>
-      <c r="U15" s="23" t="n"/>
-      <c r="V15" s="23" t="n"/>
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:17:49</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>122.7720900641192</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>101.4869</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I15" s="23" t="n">
+        <v>69.67819706498952</v>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>2.337539487642346</v>
+      </c>
+      <c r="K15" s="23" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="L15" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M15" s="23" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="N15" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O15" s="23" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="P15" s="23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q15" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R15" s="23" t="n">
+        <v>72.83799999999999</v>
+      </c>
+      <c r="S15" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T15" s="23" t="n">
+        <v>3988.38</v>
+      </c>
+      <c r="U15" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V15" s="23" t="n">
+        <v>-0.09</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1760,28 +1760,74 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="23" t="n"/>
-      <c r="G16" s="23" t="n"/>
-      <c r="H16" s="23" t="n"/>
-      <c r="I16" s="23" t="n"/>
-      <c r="J16" s="23" t="n"/>
-      <c r="K16" s="23" t="n"/>
-      <c r="L16" s="23" t="n"/>
-      <c r="M16" s="23" t="n"/>
-      <c r="N16" s="23" t="n"/>
-      <c r="O16" s="23" t="n"/>
-      <c r="P16" s="23" t="n"/>
-      <c r="Q16" s="24" t="n"/>
-      <c r="R16" s="23" t="n"/>
-      <c r="S16" s="23" t="n"/>
-      <c r="T16" s="23" t="n"/>
-      <c r="U16" s="23" t="n"/>
-      <c r="V16" s="23" t="n"/>
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:03:12</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>122.7720900641192</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>101.5425</v>
+      </c>
+      <c r="H16" s="23" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="I16" s="23" t="n">
+        <v>69.79625087596357</v>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>2.334954841961517</v>
+      </c>
+      <c r="K16" s="23" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="L16" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M16" s="23" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="N16" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O16" s="23" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="P16" s="23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q16" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R16" s="23" t="n">
+        <v>72.747</v>
+      </c>
+      <c r="S16" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T16" s="23" t="n">
+        <v>3983.97</v>
+      </c>
+      <c r="U16" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V16" s="23" t="n">
+        <v>-0.03</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1830,28 +1830,74 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="23" t="n"/>
-      <c r="G17" s="23" t="n"/>
-      <c r="H17" s="23" t="n"/>
-      <c r="I17" s="23" t="n"/>
-      <c r="J17" s="23" t="n"/>
-      <c r="K17" s="23" t="n"/>
-      <c r="L17" s="23" t="n"/>
-      <c r="M17" s="23" t="n"/>
-      <c r="N17" s="23" t="n"/>
-      <c r="O17" s="23" t="n"/>
-      <c r="P17" s="23" t="n"/>
-      <c r="Q17" s="24" t="n"/>
-      <c r="R17" s="23" t="n"/>
-      <c r="S17" s="23" t="n"/>
-      <c r="T17" s="23" t="n"/>
-      <c r="U17" s="23" t="n"/>
-      <c r="V17" s="23" t="n"/>
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-26 13:07:30</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>101.3935</v>
+      </c>
+      <c r="H17" s="23" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I17" s="23" t="n">
+        <v>71.15261756876663</v>
+      </c>
+      <c r="J17" s="23" t="n">
+        <v>2.349888350339638</v>
+      </c>
+      <c r="K17" s="23" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="L17" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M17" s="23" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="N17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="23" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="P17" s="23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q17" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R17" s="23" t="n">
+        <v>74.05800000000001</v>
+      </c>
+      <c r="S17" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T17" s="23" t="n">
+        <v>4009.45</v>
+      </c>
+      <c r="U17" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V17" s="23" t="n">
+        <v>-0.06</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1900,28 +1900,74 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="23" t="n"/>
-      <c r="G18" s="23" t="n"/>
-      <c r="H18" s="23" t="n"/>
-      <c r="I18" s="23" t="n"/>
-      <c r="J18" s="23" t="n"/>
-      <c r="K18" s="23" t="n"/>
-      <c r="L18" s="23" t="n"/>
-      <c r="M18" s="23" t="n"/>
-      <c r="N18" s="23" t="n"/>
-      <c r="O18" s="23" t="n"/>
-      <c r="P18" s="23" t="n"/>
-      <c r="Q18" s="24" t="n"/>
-      <c r="R18" s="23" t="n"/>
-      <c r="S18" s="23" t="n"/>
-      <c r="T18" s="23" t="n"/>
-      <c r="U18" s="23" t="n"/>
-      <c r="V18" s="23" t="n"/>
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-27 12:52:40</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>101.3565</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I18" s="23" t="n">
+        <v>69.44053088310362</v>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>2.391834629563423</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="L18" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M18" s="23" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="N18" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O18" s="23" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="P18" s="23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q18" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R18" s="23" t="n">
+        <v>73.416</v>
+      </c>
+      <c r="S18" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T18" s="23" t="n">
+        <v>4081.02</v>
+      </c>
+      <c r="U18" s="23" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="V18" s="23" t="n">
+        <v>-0.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -1970,28 +1970,74 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="23" t="n"/>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="23" t="n"/>
-      <c r="G19" s="23" t="n"/>
-      <c r="H19" s="23" t="n"/>
-      <c r="I19" s="23" t="n"/>
-      <c r="J19" s="23" t="n"/>
-      <c r="K19" s="23" t="n"/>
-      <c r="L19" s="23" t="n"/>
-      <c r="M19" s="23" t="n"/>
-      <c r="N19" s="23" t="n"/>
-      <c r="O19" s="23" t="n"/>
-      <c r="P19" s="23" t="n"/>
-      <c r="Q19" s="24" t="n"/>
-      <c r="R19" s="23" t="n"/>
-      <c r="S19" s="23" t="n"/>
-      <c r="T19" s="23" t="n"/>
-      <c r="U19" s="23" t="n"/>
-      <c r="V19" s="23" t="n"/>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-28 13:16:06</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C19" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D19" s="23" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>101.3565</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I19" s="23" t="n">
+        <v>69.44053088310362</v>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>2.391834629563423</v>
+      </c>
+      <c r="K19" s="23" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="L19" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M19" s="23" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="N19" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O19" s="23" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="P19" s="23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q19" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R19" s="23" t="n">
+        <v>73.416</v>
+      </c>
+      <c r="S19" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T19" s="23" t="n">
+        <v>4081.02</v>
+      </c>
+      <c r="U19" s="23" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="V19" s="23" t="n">
+        <v>-0.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -2040,28 +2040,74 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="23" t="n"/>
-      <c r="G20" s="23" t="n"/>
-      <c r="H20" s="23" t="n"/>
-      <c r="I20" s="23" t="n"/>
-      <c r="J20" s="23" t="n"/>
-      <c r="K20" s="23" t="n"/>
-      <c r="L20" s="23" t="n"/>
-      <c r="M20" s="23" t="n"/>
-      <c r="N20" s="23" t="n"/>
-      <c r="O20" s="23" t="n"/>
-      <c r="P20" s="23" t="n"/>
-      <c r="Q20" s="24" t="n"/>
-      <c r="R20" s="23" t="n"/>
-      <c r="S20" s="23" t="n"/>
-      <c r="T20" s="23" t="n"/>
-      <c r="U20" s="23" t="n"/>
-      <c r="V20" s="23" t="n"/>
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:48:54</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>101.3006</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>69.6005840920804</v>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>2.374504023490385</v>
+      </c>
+      <c r="K20" s="23" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="L20" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M20" s="23" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="N20" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O20" s="23" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="P20" s="23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q20" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R20" s="23" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="S20" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T20" s="23" t="n">
+        <v>4051.45</v>
+      </c>
+      <c r="U20" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V20" s="23" t="n">
+        <v>-0.06</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -2110,28 +2110,74 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="23" t="n"/>
-      <c r="H21" s="23" t="n"/>
-      <c r="I21" s="23" t="n"/>
-      <c r="J21" s="23" t="n"/>
-      <c r="K21" s="23" t="n"/>
-      <c r="L21" s="23" t="n"/>
-      <c r="M21" s="23" t="n"/>
-      <c r="N21" s="23" t="n"/>
-      <c r="O21" s="23" t="n"/>
-      <c r="P21" s="23" t="n"/>
-      <c r="Q21" s="24" t="n"/>
-      <c r="R21" s="23" t="n"/>
-      <c r="S21" s="23" t="n"/>
-      <c r="T21" s="23" t="n"/>
-      <c r="U21" s="23" t="n"/>
-      <c r="V21" s="23" t="n"/>
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:02:08</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>101.3875</v>
+      </c>
+      <c r="H21" s="23" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I21" s="23" t="n">
+        <v>69.1559680777238</v>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>2.336232512615533</v>
+      </c>
+      <c r="K21" s="23" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="L21" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M21" s="23" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="N21" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O21" s="23" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="P21" s="23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q21" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R21" s="23" t="n">
+        <v>73.285</v>
+      </c>
+      <c r="S21" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T21" s="23" t="n">
+        <v>3986.15</v>
+      </c>
+      <c r="U21" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V21" s="23" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="n"/>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -2180,28 +2180,74 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n"/>
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="23" t="n"/>
-      <c r="G22" s="23" t="n"/>
-      <c r="H22" s="23" t="n"/>
-      <c r="I22" s="23" t="n"/>
-      <c r="J22" s="23" t="n"/>
-      <c r="K22" s="23" t="n"/>
-      <c r="L22" s="23" t="n"/>
-      <c r="M22" s="23" t="n"/>
-      <c r="N22" s="23" t="n"/>
-      <c r="O22" s="23" t="n"/>
-      <c r="P22" s="23" t="n"/>
-      <c r="Q22" s="24" t="n"/>
-      <c r="R22" s="23" t="n"/>
-      <c r="S22" s="23" t="n"/>
-      <c r="T22" s="23" t="n"/>
-      <c r="U22" s="23" t="n"/>
-      <c r="V22" s="23" t="n"/>
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:20:32</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G22" s="23" t="n">
+        <v>101.2764</v>
+      </c>
+      <c r="H22" s="23" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I22" s="23" t="n">
+        <v>69.03127715030409</v>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>2.328378940705532</v>
+      </c>
+      <c r="K22" s="23" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="L22" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M22" s="23" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="N22" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O22" s="23" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="P22" s="23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q22" s="24" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="R22" s="23" t="n">
+        <v>73.197</v>
+      </c>
+      <c r="S22" s="23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T22" s="23" t="n">
+        <v>3972.75</v>
+      </c>
+      <c r="U22" s="23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V22" s="23" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -2249,6 +2249,76 @@
         <v>0.11</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-02 12:56:32</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D23" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>101.326</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="I23" t="n">
+        <v>67.62506240639041</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.381619125205863</v>
+      </c>
+      <c r="K23" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="L23" t="n">
+        <v>50</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="N23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O23" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R23" t="n">
+        <v>70.852</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4063.59</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -2319,6 +2319,76 @@
         <v>-0.09</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-03 12:40:37</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D24" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100.7764</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="I24" t="n">
+        <v>66.96632996632997</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.44790561647609</v>
+      </c>
+      <c r="K24" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="L24" t="n">
+        <v>50</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N24" t="n">
+        <v>50</v>
+      </c>
+      <c r="O24" t="n">
+        <v>22.040001</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R24" t="n">
+        <v>72.288</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4176.69</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2415,6 +2415,76 @@
         <is>
           <t>Fed预期差: 正数=预期降息bp, 负数=预期加息bp</t>
         </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-04 12:33:56</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D29" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G29" t="n">
+        <v>100.8657</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="I29" t="n">
+        <v>66.94627966645287</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.446780328560628</v>
+      </c>
+      <c r="K29" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="L29" t="n">
+        <v>50</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N29" t="n">
+        <v>50</v>
+      </c>
+      <c r="O29" t="n">
+        <v>22.040001</v>
+      </c>
+      <c r="P29" t="n">
+        <v/>
+      </c>
+      <c r="Q29" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R29" t="n">
+        <v>71.995</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4174.77</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2465,9 +2465,6 @@
       <c r="O29" t="n">
         <v>22.040001</v>
       </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="n">
         <v>173.64</v>
       </c>
@@ -2484,6 +2481,76 @@
         <v>-0.01</v>
       </c>
       <c r="V29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:55:29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D30" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>100.8657</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="I30" t="n">
+        <v>66.94627966645287</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.446780328560628</v>
+      </c>
+      <c r="K30" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="L30" t="n">
+        <v>50</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N30" t="n">
+        <v>50</v>
+      </c>
+      <c r="O30" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="P30" t="n">
+        <v/>
+      </c>
+      <c r="Q30" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R30" t="n">
+        <v>71.995</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4174.77</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2532,9 +2532,6 @@
       <c r="O30" t="n">
         <v>22.24</v>
       </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="n">
         <v>173.64</v>
       </c>
@@ -2552,6 +2549,76 @@
       </c>
       <c r="V30" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:55:53</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D31" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G31" t="n">
+        <v>100.9489</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="I31" t="n">
+        <v>67.30948527031401</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.437174355157277</v>
+      </c>
+      <c r="K31" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="L31" t="n">
+        <v>50</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N31" t="n">
+        <v>50</v>
+      </c>
+      <c r="O31" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="P31" t="n">
+        <v/>
+      </c>
+      <c r="Q31" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R31" t="n">
+        <v>71.81100000000001</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4158.38</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2599,9 +2599,6 @@
       <c r="O31" t="n">
         <v>22.24</v>
       </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="n">
         <v>173.64</v>
       </c>
@@ -2619,6 +2616,76 @@
       </c>
       <c r="V31" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-06 13:09:11</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D32" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G32" t="n">
+        <v>100.9831</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="I32" t="n">
+        <v>67.28511258707275</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.434320109246702</v>
+      </c>
+      <c r="K32" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="L32" t="n">
+        <v>50</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N32" t="n">
+        <v>50</v>
+      </c>
+      <c r="O32" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="P32" t="n">
+        <v/>
+      </c>
+      <c r="Q32" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R32" t="n">
+        <v>72</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4153.51</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2666,9 +2666,6 @@
       <c r="O32" t="n">
         <v>22.24</v>
       </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="n">
         <v>173.64</v>
       </c>
@@ -2686,6 +2683,76 @@
       </c>
       <c r="V32" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:51:21</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D33" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G33" t="n">
+        <v>100.8592</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="I33" t="n">
+        <v>67.7481542247744</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.420101627564865</v>
+      </c>
+      <c r="K33" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>50</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="N33" t="n">
+        <v>50</v>
+      </c>
+      <c r="O33" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R33" t="n">
+        <v>72.52200000000001</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4129.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2753,6 +2753,76 @@
       </c>
       <c r="V33" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:13:21</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D34" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G34" t="n">
+        <v>101.1102</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="I34" t="n">
+        <v>68.3762015246934</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.418091347590887</v>
+      </c>
+      <c r="K34" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>50</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="N34" t="n">
+        <v>50</v>
+      </c>
+      <c r="O34" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R34" t="n">
+        <v>76.143</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4125.82</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2823,6 +2823,76 @@
       </c>
       <c r="V34" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:51:15</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D35" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>100.9757</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="I35" t="n">
+        <v>70.11183983431137</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.380851350638542</v>
+      </c>
+      <c r="K35" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="L35" t="n">
+        <v>50</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="N35" t="n">
+        <v>50</v>
+      </c>
+      <c r="O35" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R35" t="n">
+        <v>78.89700000000001</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4062.28</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2893,6 +2893,76 @@
       </c>
       <c r="V35" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:50:40</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D36" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G36" t="n">
+        <v>100.7793</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="I36" t="n">
+        <v>68.19711777372868</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.412957221476589</v>
+      </c>
+      <c r="K36" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="L36" t="n">
+        <v>50</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="N36" t="n">
+        <v>50</v>
+      </c>
+      <c r="O36" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R36" t="n">
+        <v>76.565</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4117.06</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-0.15</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2963,6 +2963,76 @@
       </c>
       <c r="V36" t="n">
         <v>-0.15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:11:44</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D37" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G37" t="n">
+        <v>100.9609</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="I37" t="n">
+        <v>68.83372326203208</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.414100092015731</v>
+      </c>
+      <c r="K37" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="L37" t="n">
+        <v>50</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="N37" t="n">
+        <v>50</v>
+      </c>
+      <c r="O37" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R37" t="n">
+        <v>75.229</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4119.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3032,6 +3032,76 @@
         <v>-0.02</v>
       </c>
       <c r="V37" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-12 12:24:23</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D38" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G38" t="n">
+        <v>100.9609</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="I38" t="n">
+        <v>68.83372326203208</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.414100092015731</v>
+      </c>
+      <c r="K38" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="L38" t="n">
+        <v>50</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="N38" t="n">
+        <v>50</v>
+      </c>
+      <c r="O38" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R38" t="n">
+        <v>75.229</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4119.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="V38" t="n">
         <v>0.03</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3103,6 +3103,76 @@
       </c>
       <c r="V38" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-13 12:29:28</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D39" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G39" t="n">
+        <v>101.108</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="I39" t="n">
+        <v>69.79579889807162</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.375846163764557</v>
+      </c>
+      <c r="K39" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="L39" t="n">
+        <v>50</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="N39" t="n">
+        <v>50</v>
+      </c>
+      <c r="O39" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R39" t="n">
+        <v>79.163</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4053.74</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3173,6 +3173,76 @@
       </c>
       <c r="V39" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-14 11:55:32</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D40" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G40" t="n">
+        <v>101.172</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="I40" t="n">
+        <v>69.67308359347902</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.354518441241802</v>
+      </c>
+      <c r="K40" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="L40" t="n">
+        <v>50</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-0.424</v>
+      </c>
+      <c r="N40" t="n">
+        <v>50</v>
+      </c>
+      <c r="O40" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R40" t="n">
+        <v>84.544</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4017.35</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V40" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3242,6 +3242,76 @@
         <v>-0.01</v>
       </c>
       <c r="V40" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:56:57</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D41" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100.7977</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="I41" t="n">
+        <v>69.03749999999999</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.362981544106011</v>
+      </c>
+      <c r="K41" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="L41" t="n">
+        <v>50</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-0.526</v>
+      </c>
+      <c r="N41" t="n">
+        <v>50</v>
+      </c>
+      <c r="O41" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R41" t="n">
+        <v>85.783</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4031.79</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V41" t="n">
         <v>-0.13</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3313,6 +3313,76 @@
       </c>
       <c r="V41" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:07:34</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D42" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100.5147</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="I42" t="n">
+        <v>70.59740941711885</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.363825510042608</v>
+      </c>
+      <c r="K42" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="L42" t="n">
+        <v>50</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-0.498</v>
+      </c>
+      <c r="N42" t="n">
+        <v>50</v>
+      </c>
+      <c r="O42" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R42" t="n">
+        <v>84.756</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4033.23</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3383,6 +3383,76 @@
       </c>
       <c r="V42" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-17 11:58:34</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D43" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G43" t="n">
+        <v>100.7602</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="I43" t="n">
+        <v>72.0588553890594</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.339274306512018</v>
+      </c>
+      <c r="K43" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>50</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="N43" t="n">
+        <v>50</v>
+      </c>
+      <c r="O43" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R43" t="n">
+        <v>85.01300000000001</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3991.34</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3452,6 +3452,76 @@
         <v>-0.01</v>
       </c>
       <c r="V43" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-18 11:53:37</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D44" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G44" t="n">
+        <v>100.7617</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="I44" t="n">
+        <v>71.86187153336913</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.353938214660392</v>
+      </c>
+      <c r="K44" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="L44" t="n">
+        <v>50</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-0.422</v>
+      </c>
+      <c r="N44" t="n">
+        <v>50</v>
+      </c>
+      <c r="O44" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R44" t="n">
+        <v>88.273</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4016.36</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="V44" t="n">
         <v>0.04</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3522,6 +3522,76 @@
         <v>-0.02</v>
       </c>
       <c r="V44" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:22:42</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D45" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G45" t="n">
+        <v>100.7617</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="I45" t="n">
+        <v>71.86187153336913</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.353938214660392</v>
+      </c>
+      <c r="K45" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="L45" t="n">
+        <v>50</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-0.422</v>
+      </c>
+      <c r="N45" t="n">
+        <v>50</v>
+      </c>
+      <c r="O45" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R45" t="n">
+        <v>88.273</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4016.36</v>
+      </c>
+      <c r="U45" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="V45" t="n">
         <v>0.04</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3593,6 +3593,76 @@
       </c>
       <c r="V45" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:34:40</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D46" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100.6961</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="I46" t="n">
+        <v>70.64389815627743</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.357929470235549</v>
+      </c>
+      <c r="K46" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="L46" t="n">
+        <v>50</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-0.422</v>
+      </c>
+      <c r="N46" t="n">
+        <v>50</v>
+      </c>
+      <c r="O46" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R46" t="n">
+        <v>90.43899999999999</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4023.17</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V46" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3663,6 +3663,76 @@
       </c>
       <c r="V46" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-21 12:14:05</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D47" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G47" t="n">
+        <v>100.9603</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="I47" t="n">
+        <v>69.98996713371389</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.371380177350064</v>
+      </c>
+      <c r="K47" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="L47" t="n">
+        <v>50</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-0.228</v>
+      </c>
+      <c r="N47" t="n">
+        <v>50</v>
+      </c>
+      <c r="O47" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R47" t="n">
+        <v>88.43300000000001</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4046.12</v>
+      </c>
+      <c r="U47" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V47" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3733,6 +3733,76 @@
       </c>
       <c r="V47" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-22 12:15:31</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D48" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G48" t="n">
+        <v>101.1504</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="I48" t="n">
+        <v>69.11319490957803</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.419040809269559</v>
+      </c>
+      <c r="K48" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="L48" t="n">
+        <v>50</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-0.272</v>
+      </c>
+      <c r="N48" t="n">
+        <v>50</v>
+      </c>
+      <c r="O48" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R48" t="n">
+        <v>92.26000000000001</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4127.44</v>
+      </c>
+      <c r="U48" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V48" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3803,6 +3803,76 @@
       </c>
       <c r="V48" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-23 12:14:27</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D49" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G49" t="n">
+        <v>100.949</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="I49" t="n">
+        <v>68.96590909090909</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.418736043792455</v>
+      </c>
+      <c r="K49" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="L49" t="n">
+        <v>50</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-0.286</v>
+      </c>
+      <c r="N49" t="n">
+        <v>50</v>
+      </c>
+      <c r="O49" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R49" t="n">
+        <v>91.60599999999999</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4126.92</v>
+      </c>
+      <c r="U49" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V49" t="n">
+        <v>-0.17</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V49"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3873,6 +3873,76 @@
       </c>
       <c r="V49" t="n">
         <v>-0.17</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-24 12:12:52</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D50" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G50" t="n">
+        <v>101.4056</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I50" t="n">
+        <v>70.41566159762279</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.256232182762155</v>
+      </c>
+      <c r="K50" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="L50" t="n">
+        <v>50</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-0.354</v>
+      </c>
+      <c r="N50" t="n">
+        <v>50</v>
+      </c>
+      <c r="O50" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R50" t="n">
+        <v>93.792</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4028.48</v>
+      </c>
+      <c r="U50" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V50" t="n">
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3943,6 +3943,76 @@
       </c>
       <c r="V50" t="n">
         <v>-0.04</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-25 12:08:44</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D51" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G51" t="n">
+        <v>101.4647</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I51" t="n">
+        <v>69.66809900309384</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.270127528017519</v>
+      </c>
+      <c r="K51" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="L51" t="n">
+        <v>50</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-0.648</v>
+      </c>
+      <c r="N51" t="n">
+        <v>50</v>
+      </c>
+      <c r="O51" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R51" t="n">
+        <v>92.95399999999999</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4053.29</v>
+      </c>
+      <c r="U51" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:V52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4012,6 +4012,76 @@
         <v>-0.01</v>
       </c>
       <c r="V51" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-26 12:24:25</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D52" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G52" t="n">
+        <v>101.4647</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I52" t="n">
+        <v>69.66809900309384</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.270127528017519</v>
+      </c>
+      <c r="K52" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="L52" t="n">
+        <v>50</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-0.648</v>
+      </c>
+      <c r="N52" t="n">
+        <v>50</v>
+      </c>
+      <c r="O52" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R52" t="n">
+        <v>92.95399999999999</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4053.29</v>
+      </c>
+      <c r="U52" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V52" t="n">
         <v>0.02</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4083,6 +4083,76 @@
       </c>
       <c r="V52" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:35:35</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C53" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D53" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G53" t="n">
+        <v>101.211</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I53" t="n">
+        <v>69.02632467094162</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.290967745548841</v>
+      </c>
+      <c r="K53" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="L53" t="n">
+        <v>50</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-0.648</v>
+      </c>
+      <c r="N53" t="n">
+        <v>50</v>
+      </c>
+      <c r="O53" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R53" t="n">
+        <v>87.69</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4090.5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V53" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4153,6 +4153,76 @@
       </c>
       <c r="V53" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-28 12:07:10</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D54" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G54" t="n">
+        <v>101.4988</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I54" t="n">
+        <v>70.62663641124105</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.266156629272637</v>
+      </c>
+      <c r="K54" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="L54" t="n">
+        <v>50</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-0.742</v>
+      </c>
+      <c r="N54" t="n">
+        <v>50</v>
+      </c>
+      <c r="O54" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R54" t="n">
+        <v>84.928</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4046.2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V54" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4223,6 +4223,76 @@
       </c>
       <c r="V54" t="n">
         <v>-0.03</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:10:31</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D55" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G55" t="n">
+        <v>101.3056</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="I55" t="n">
+        <v>70.13653007846555</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.252787750141418</v>
+      </c>
+      <c r="K55" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="L55" t="n">
+        <v>50</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-0.764</v>
+      </c>
+      <c r="N55" t="n">
+        <v>50</v>
+      </c>
+      <c r="O55" t="n">
+        <v>22.030001</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R55" t="n">
+        <v>85.20699999999999</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4022.33</v>
+      </c>
+      <c r="U55" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V55" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V55"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4293,6 +4293,73 @@
       </c>
       <c r="V55" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:55:28</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D56" t="n">
+        <v>122.5938713264953</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G56" t="n">
+        <v>100.9416</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.272614240348588</v>
+      </c>
+      <c r="K56" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="L56" t="n">
+        <v>50</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N56" t="n">
+        <v>50</v>
+      </c>
+      <c r="O56" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R56" t="n">
+        <v>87.252</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4057.73</v>
+      </c>
+      <c r="U56" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4360,6 +4360,76 @@
       </c>
       <c r="V56" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:28:18</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D57" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G57" t="n">
+        <v>99.7206</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="I57" t="n">
+        <v>69.7073337902673</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.278433371231427</v>
+      </c>
+      <c r="K57" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="L57" t="n">
+        <v>50</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-0.636</v>
+      </c>
+      <c r="N57" t="n">
+        <v>50</v>
+      </c>
+      <c r="O57" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="R57" t="n">
+        <v>83.494</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4068.12</v>
+      </c>
+      <c r="U57" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V57" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4430,6 +4430,76 @@
       </c>
       <c r="V57" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-04 12:12:13</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D58" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="G58" t="n">
+        <v>100.0225</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I58" t="n">
+        <v>69.05825242718446</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.270754806803735</v>
+      </c>
+      <c r="K58" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="L58" t="n">
+        <v>50</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-0.544</v>
+      </c>
+      <c r="N58" t="n">
+        <v>50</v>
+      </c>
+      <c r="O58" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R58" t="n">
+        <v>85.014</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4054.41</v>
+      </c>
+      <c r="U58" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:V59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4500,6 +4500,76 @@
       </c>
       <c r="V58" t="n">
         <v>0.06</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:59:11</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D59" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G59" t="n">
+        <v>99.8009</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I59" t="n">
+        <v>67.97612775765558</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.312457644680172</v>
+      </c>
+      <c r="K59" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="L59" t="n">
+        <v>50</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="N59" t="n">
+        <v>50</v>
+      </c>
+      <c r="O59" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R59" t="n">
+        <v>78.33199999999999</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4128.87</v>
+      </c>
+      <c r="U59" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V59" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V59"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4570,6 +4570,76 @@
       </c>
       <c r="V59" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-06 12:10:40</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D60" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G60" t="n">
+        <v>99.72280000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I60" t="n">
+        <v>68.63256113256114</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.389372105136405</v>
+      </c>
+      <c r="K60" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="L60" t="n">
+        <v>50</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-0.482</v>
+      </c>
+      <c r="N60" t="n">
+        <v>50</v>
+      </c>
+      <c r="O60" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R60" t="n">
+        <v>79.17400000000001</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4266.2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4640,6 +4640,76 @@
       </c>
       <c r="V60" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-07 11:48:34</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D61" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G61" t="n">
+        <v>99.9652</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I61" t="n">
+        <v>68.42611628654032</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.386017283770842</v>
+      </c>
+      <c r="K61" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="L61" t="n">
+        <v>50</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-0.462</v>
+      </c>
+      <c r="N61" t="n">
+        <v>50</v>
+      </c>
+      <c r="O61" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R61" t="n">
+        <v>83.402</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4260.21</v>
+      </c>
+      <c r="U61" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4710,6 +4710,76 @@
       </c>
       <c r="V61" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-08 10:53:15</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D62" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G62" t="n">
+        <v>99.5996</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I62" t="n">
+        <v>68.34256926952141</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.431332575371467</v>
+      </c>
+      <c r="K62" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L62" t="n">
+        <v>50</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="N62" t="n">
+        <v>50</v>
+      </c>
+      <c r="O62" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R62" t="n">
+        <v>82.301</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4341.12</v>
+      </c>
+      <c r="U62" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V62" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V62"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4779,6 +4779,76 @@
         <v>-0.01</v>
       </c>
       <c r="V62" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:01:05</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D63" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G63" t="n">
+        <v>99.5996</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I63" t="n">
+        <v>68.34256926952141</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.431332575371467</v>
+      </c>
+      <c r="K63" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L63" t="n">
+        <v>50</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="N63" t="n">
+        <v>50</v>
+      </c>
+      <c r="O63" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R63" t="n">
+        <v>82.301</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4341.12</v>
+      </c>
+      <c r="U63" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V63" t="n">
         <v>-0.34</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4850,6 +4850,76 @@
       </c>
       <c r="V63" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:10:16</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D64" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G64" t="n">
+        <v>99.7163</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I64" t="n">
+        <v>68.2465623518255</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.418361346185081</v>
+      </c>
+      <c r="K64" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L64" t="n">
+        <v>50</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="N64" t="n">
+        <v>50</v>
+      </c>
+      <c r="O64" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R64" t="n">
+        <v>84.142</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4317.96</v>
+      </c>
+      <c r="U64" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V64"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4920,6 +4920,76 @@
       </c>
       <c r="V64" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-11 11:03:07</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D65" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G65" t="n">
+        <v>99.81950000000001</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I65" t="n">
+        <v>67.05423883318142</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2.471876067634095</v>
+      </c>
+      <c r="K65" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="L65" t="n">
+        <v>50</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-0.206</v>
+      </c>
+      <c r="N65" t="n">
+        <v>50</v>
+      </c>
+      <c r="O65" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R65" t="n">
+        <v>87.937</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4413.51</v>
+      </c>
+      <c r="U65" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4990,6 +4990,76 @@
       </c>
       <c r="V65" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:21:58</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D66" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G66" t="n">
+        <v>99.86199999999999</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I66" t="n">
+        <v>67.28370743624981</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.467899568185764</v>
+      </c>
+      <c r="K66" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="L66" t="n">
+        <v>50</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-0.102</v>
+      </c>
+      <c r="N66" t="n">
+        <v>50</v>
+      </c>
+      <c r="O66" t="n">
+        <v>20.049999</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R66" t="n">
+        <v>89.73999999999999</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4406.41</v>
+      </c>
+      <c r="U66" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V66"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5060,6 +5060,76 @@
       </c>
       <c r="V66" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:23:00</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D67" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G67" t="n">
+        <v>99.87130000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I67" t="n">
+        <v>67.53091817613991</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2.422125018902374</v>
+      </c>
+      <c r="K67" t="n">
+        <v>51.91</v>
+      </c>
+      <c r="L67" t="n">
+        <v>50</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="N67" t="n">
+        <v>50</v>
+      </c>
+      <c r="O67" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R67" t="n">
+        <v>87.053</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4324.68</v>
+      </c>
+      <c r="U67" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V67" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5130,6 +5130,76 @@
       </c>
       <c r="V67" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:12:43</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D68" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G68" t="n">
+        <v>99.6391</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I68" t="n">
+        <v>67.66352249884027</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2.450755814930355</v>
+      </c>
+      <c r="K68" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="L68" t="n">
+        <v>50</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N68" t="n">
+        <v>50</v>
+      </c>
+      <c r="O68" t="n">
+        <v>19.355</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R68" t="n">
+        <v>88.833</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4375.8</v>
+      </c>
+      <c r="U68" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V68" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5199,6 +5199,76 @@
         <v>-0.01</v>
       </c>
       <c r="V68" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:20:05</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D69" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G69" t="n">
+        <v>99.6391</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I69" t="n">
+        <v>67.66352249884027</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2.450755814930355</v>
+      </c>
+      <c r="K69" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="L69" t="n">
+        <v>50</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N69" t="n">
+        <v>50</v>
+      </c>
+      <c r="O69" t="n">
+        <v>19.355</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R69" t="n">
+        <v>88.833</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4375.8</v>
+      </c>
+      <c r="U69" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V69" t="n">
         <v>-0.32</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V69"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5270,6 +5270,76 @@
       </c>
       <c r="V69" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:18:49</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D70" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G70" t="n">
+        <v>99.5038</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I70" t="n">
+        <v>66.87304003653524</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2.460327417123591</v>
+      </c>
+      <c r="K70" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="L70" t="n">
+        <v>50</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N70" t="n">
+        <v>50</v>
+      </c>
+      <c r="O70" t="n">
+        <v>19.355</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R70" t="n">
+        <v>89.236</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4392.89</v>
+      </c>
+      <c r="U70" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V70" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5340,6 +5340,76 @@
       </c>
       <c r="V70" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:14:32</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C71" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D71" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G71" t="n">
+        <v>99.5997</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="I71" t="n">
+        <v>67.27021244077639</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.465144022089174</v>
+      </c>
+      <c r="K71" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="N71" t="n">
+        <v>50</v>
+      </c>
+      <c r="O71" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R71" t="n">
+        <v>91.244</v>
+      </c>
+      <c r="S71" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4401.49</v>
+      </c>
+      <c r="U71" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V71"/>
+  <dimension ref="A1:V72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5410,6 +5410,76 @@
       </c>
       <c r="V71" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:17:00</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D72" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G72" t="n">
+        <v>99.5681</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I72" t="n">
+        <v>68.98305889803675</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2.440209690337106</v>
+      </c>
+      <c r="K72" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-0.122</v>
+      </c>
+      <c r="N72" t="n">
+        <v>50</v>
+      </c>
+      <c r="O72" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R72" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4356.97</v>
+      </c>
+      <c r="U72" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V72" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V72"/>
+  <dimension ref="A1:V73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5480,6 +5480,76 @@
       </c>
       <c r="V72" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:16:07</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D73" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G73" t="n">
+        <v>98.8407</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I73" t="n">
+        <v>66.87356834746393</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2.518025864048524</v>
+      </c>
+      <c r="K73" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="N73" t="n">
+        <v>50</v>
+      </c>
+      <c r="O73" t="n">
+        <v>19.049999</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R73" t="n">
+        <v>92.069</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4495.91</v>
+      </c>
+      <c r="U73" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5550,6 +5550,76 @@
       </c>
       <c r="V73" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:22:05</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D74" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G74" t="n">
+        <v>98.76609999999999</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I74" t="n">
+        <v>66.09338009644893</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.533069353510801</v>
+      </c>
+      <c r="K74" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="N74" t="n">
+        <v>50</v>
+      </c>
+      <c r="O74" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R74" t="n">
+        <v>93.798</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4522.77</v>
+      </c>
+      <c r="U74" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V74" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5620,6 +5620,76 @@
       </c>
       <c r="V74" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-22 10:14:31</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D75" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>98.84610000000001</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I75" t="n">
+        <v>66.76134551254168</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2.578860704904536</v>
+      </c>
+      <c r="K75" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="N75" t="n">
+        <v>50</v>
+      </c>
+      <c r="O75" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R75" t="n">
+        <v>92.304</v>
+      </c>
+      <c r="S75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4604.53</v>
+      </c>
+      <c r="U75" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V75" t="n">
+        <v>-0.02</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5689,6 +5689,76 @@
         <v>-0.01</v>
       </c>
       <c r="V75" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-23 10:22:52</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D76" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G76" t="n">
+        <v>98.84610000000001</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I76" t="n">
+        <v>66.76134551254168</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.578860704904536</v>
+      </c>
+      <c r="K76" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="N76" t="n">
+        <v>50</v>
+      </c>
+      <c r="O76" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R76" t="n">
+        <v>92.304</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4604.53</v>
+      </c>
+      <c r="U76" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V76" t="n">
         <v>-0.02</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5760,6 +5760,76 @@
       </c>
       <c r="V76" t="n">
         <v>-0.02</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:21:21</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D77" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G77" t="n">
+        <v>98.80159999999999</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I77" t="n">
+        <v>67.17270758122744</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2.605284823773866</v>
+      </c>
+      <c r="K77" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="N77" t="n">
+        <v>50</v>
+      </c>
+      <c r="O77" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R77" t="n">
+        <v>90.896</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4651.71</v>
+      </c>
+      <c r="U77" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V77" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V77"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5830,6 +5830,76 @@
       </c>
       <c r="V77" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:16:52</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C78" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D78" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G78" t="n">
+        <v>99.01690000000001</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="I78" t="n">
+        <v>68.15304475421863</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2.601319525732432</v>
+      </c>
+      <c r="K78" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="N78" t="n">
+        <v>50</v>
+      </c>
+      <c r="O78" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R78" t="n">
+        <v>91.155</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4644.63</v>
+      </c>
+      <c r="U78" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V78"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5900,6 +5900,76 @@
       </c>
       <c r="V78" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:23:27</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D79" t="n">
+        <v>120.2930512227635</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G79" t="n">
+        <v>98.9152</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="I79" t="n">
+        <v>67.12791702679344</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2.609939008339448</v>
+      </c>
+      <c r="K79" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R79" t="n">
+        <v>85.288</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4660.02</v>
+      </c>
+      <c r="U79" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5970,6 +5970,76 @@
       </c>
       <c r="V79" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:54:03</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D80" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G80" t="n">
+        <v>99.24299999999999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I80" t="n">
+        <v>67.14749780509217</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2.570084402600966</v>
+      </c>
+      <c r="K80" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="L80" t="n">
+        <v>50</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="N80" t="n">
+        <v>50</v>
+      </c>
+      <c r="O80" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="P80" t="n">
+        <v/>
+      </c>
+      <c r="Q80" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R80" t="n">
+        <v>87.37</v>
+      </c>
+      <c r="S80" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4588.86</v>
+      </c>
+      <c r="U80" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6020,9 +6020,6 @@
       <c r="O80" t="n">
         <v>18.54</v>
       </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="n">
         <v>152.67</v>
       </c>
@@ -6040,6 +6037,76 @@
       </c>
       <c r="V80" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:29:44</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D81" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G81" t="n">
+        <v>99.2115</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I81" t="n">
+        <v>65.22100935639352</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2.576710034780368</v>
+      </c>
+      <c r="K81" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="L81" t="n">
+        <v>50</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N81" t="n">
+        <v>50</v>
+      </c>
+      <c r="O81" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="P81" t="n">
+        <v/>
+      </c>
+      <c r="Q81" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R81" t="n">
+        <v>87.78700000000001</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>4600.69</v>
+      </c>
+      <c r="U81" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6087,9 +6087,6 @@
       <c r="O81" t="n">
         <v>18.1</v>
       </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="n">
         <v>152.67</v>
       </c>
@@ -6107,6 +6104,76 @@
       </c>
       <c r="V81" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-29 15:39:07</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C82" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D82" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G82" t="n">
+        <v>99.6831</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I82" t="n">
+        <v>67.18295625942685</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2.494682132075789</v>
+      </c>
+      <c r="K82" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="L82" t="n">
+        <v>50</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="N82" t="n">
+        <v>50</v>
+      </c>
+      <c r="O82" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R82" t="n">
+        <v>88.331</v>
+      </c>
+      <c r="S82" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4454.23</v>
+      </c>
+      <c r="U82" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V82"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6173,6 +6173,76 @@
         <v>-0.02</v>
       </c>
       <c r="V82" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-30 14:13:52</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C83" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D83" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G83" t="n">
+        <v>99.6831</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I83" t="n">
+        <v>67.18295625942685</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2.494682132075789</v>
+      </c>
+      <c r="K83" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="L83" t="n">
+        <v>50</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="N83" t="n">
+        <v>50</v>
+      </c>
+      <c r="O83" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R83" t="n">
+        <v>88.331</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T83" t="n">
+        <v>4454.23</v>
+      </c>
+      <c r="U83" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="V83" t="n">
         <v>0.55</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V83"/>
+  <dimension ref="A1:V84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6244,6 +6244,76 @@
       </c>
       <c r="V83" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:39:44</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C84" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D84" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G84" t="n">
+        <v>99.6066</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I84" t="n">
+        <v>66.5476618705036</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2.486745935289473</v>
+      </c>
+      <c r="K84" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="L84" t="n">
+        <v>50</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="N84" t="n">
+        <v>50</v>
+      </c>
+      <c r="O84" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>152.67</v>
+      </c>
+      <c r="R84" t="n">
+        <v>90.63800000000001</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4440.06</v>
+      </c>
+      <c r="U84" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V84" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V84"/>
+  <dimension ref="A1:V85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6314,6 +6314,76 @@
       </c>
       <c r="V84" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:26:23</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D85" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G85" t="n">
+        <v>99.7711</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I85" t="n">
+        <v>67.53532821557262</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2.414340041109163</v>
+      </c>
+      <c r="K85" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="L85" t="n">
+        <v>50</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="N85" t="n">
+        <v>50</v>
+      </c>
+      <c r="O85" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R85" t="n">
+        <v>95.27500000000001</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T85" t="n">
+        <v>4310.78</v>
+      </c>
+      <c r="U85" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V85"/>
+  <dimension ref="A1:V86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6384,6 +6384,76 @@
       </c>
       <c r="V85" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:28:00</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D86" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G86" t="n">
+        <v>99.3822</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I86" t="n">
+        <v>67.36662606577345</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2.478109650572112</v>
+      </c>
+      <c r="K86" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="L86" t="n">
+        <v>50</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N86" t="n">
+        <v>50</v>
+      </c>
+      <c r="O86" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R86" t="n">
+        <v>94.59699999999999</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T86" t="n">
+        <v>4424.64</v>
+      </c>
+      <c r="U86" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V86" t="n">
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V86"/>
+  <dimension ref="A1:V87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6454,6 +6454,76 @@
       </c>
       <c r="V86" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-05 13:15:24</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D87" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G87" t="n">
+        <v>99.155</v>
+      </c>
+      <c r="H87" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="I87" t="n">
+        <v>66.96327640924891</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2.481649295151471</v>
+      </c>
+      <c r="K87" t="n">
+        <v>62.26</v>
+      </c>
+      <c r="L87" t="n">
+        <v>50</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N87" t="n">
+        <v>50</v>
+      </c>
+      <c r="O87" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R87" t="n">
+        <v>95.929</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T87" t="n">
+        <v>4430.96</v>
+      </c>
+      <c r="U87" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
